--- a/12610368.xlsx
+++ b/12610368.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayush\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayush\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9F3904-D8AB-43DE-B1ED-E627D90E1BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2ECF3B7-F5AA-4B30-83B7-C04600DEE950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>Had a pretty busy day, but managed to get some study done.</t>
+  </si>
+  <si>
+    <t>Bit tired day,preparing for CA and mid term</t>
   </si>
 </sst>
 </file>
@@ -2962,27 +2965,51 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+    <row r="46" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B46" s="14">
+        <v>460</v>
+      </c>
+      <c r="C46" s="14">
+        <v>70</v>
+      </c>
+      <c r="D46" s="14">
+        <v>240</v>
+      </c>
+      <c r="E46" s="14">
+        <v>145</v>
+      </c>
+      <c r="F46" s="14">
+        <v>250</v>
+      </c>
+      <c r="G46" s="14">
+        <v>5</v>
+      </c>
+      <c r="H46" s="14">
+        <v>190</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1355</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>85</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>

--- a/12610368.xlsx
+++ b/12610368.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayush\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2ECF3B7-F5AA-4B30-83B7-C04600DEE950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE97E95-34A9-4A8B-8228-B893252FDDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Bit tired day,preparing for CA and mid term</t>
+  </si>
+  <si>
+    <t>Practicing questions for anylitical to grab good marks in mid term</t>
   </si>
 </sst>
 </file>
@@ -3011,27 +3014,51 @@
         <v>103</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+    <row r="47" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B47" s="14">
+        <v>445</v>
+      </c>
+      <c r="C47" s="14">
+        <v>65</v>
+      </c>
+      <c r="D47" s="14">
+        <v>210</v>
+      </c>
+      <c r="E47" s="14">
+        <v>195</v>
+      </c>
+      <c r="F47" s="14">
+        <v>250</v>
+      </c>
+      <c r="G47" s="14">
+        <v>5</v>
+      </c>
+      <c r="H47" s="14">
+        <v>160</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1325</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>115</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>

--- a/12610368.xlsx
+++ b/12610368.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayush\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE97E95-34A9-4A8B-8228-B893252FDDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B184616D-99D5-4D81-B8DE-A1F8945207E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>Practicing questions for anylitical to grab good marks in mid term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hectic day , had 2 CAs and will prepare for their Viva for upcoming class. </t>
   </si>
 </sst>
 </file>
@@ -3060,27 +3063,51 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+    <row r="48" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B48" s="14">
+        <v>430</v>
+      </c>
+      <c r="C48" s="14">
+        <v>80</v>
+      </c>
+      <c r="D48" s="14">
+        <v>230</v>
+      </c>
+      <c r="E48" s="14">
+        <v>170</v>
+      </c>
+      <c r="F48" s="14">
+        <v>300</v>
+      </c>
+      <c r="G48" s="14">
+        <v>6</v>
+      </c>
+      <c r="H48" s="14">
+        <v>170</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>

--- a/12610368.xlsx
+++ b/12610368.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayush\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B184616D-99D5-4D81-B8DE-A1F8945207E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C766CF-5170-4D48-A3C1-12C407E29EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t xml:space="preserve">Hectic day , had 2 CAs and will prepare for their Viva for upcoming class. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long class with ca viva so preparing for that. </t>
   </si>
 </sst>
 </file>
@@ -3109,27 +3112,51 @@
         <v>105</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+    <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B49" s="14">
+        <v>480</v>
+      </c>
+      <c r="C49" s="14">
+        <v>60</v>
+      </c>
+      <c r="D49" s="14">
+        <v>190</v>
+      </c>
+      <c r="E49" s="14">
+        <v>150</v>
+      </c>
+      <c r="F49" s="14">
+        <v>300</v>
+      </c>
+      <c r="G49" s="14">
+        <v>6</v>
+      </c>
+      <c r="H49" s="14">
+        <v>140</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>

--- a/12610368.xlsx
+++ b/12610368.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayush\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C766CF-5170-4D48-A3C1-12C407E29EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C60A64-A176-498D-9C53-E31386F0EA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t xml:space="preserve">Long class with ca viva so preparing for that. </t>
+  </si>
+  <si>
+    <t>No classees , enjoyed the day</t>
   </si>
 </sst>
 </file>
@@ -3159,26 +3162,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B50" s="14">
+        <v>460</v>
+      </c>
+      <c r="C50" s="14">
+        <v>0</v>
+      </c>
+      <c r="D50" s="14">
+        <v>200</v>
+      </c>
+      <c r="E50" s="14">
+        <v>160</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>150</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>

--- a/12610368.xlsx
+++ b/12610368.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayush\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C60A64-A176-498D-9C53-E31386F0EA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075FBA50-FF38-42E2-A34D-D7D10FBEC383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -359,6 +359,12 @@
   </si>
   <si>
     <t>No classees , enjoyed the day</t>
+  </si>
+  <si>
+    <t>Protest was happening.</t>
+  </si>
+  <si>
+    <t>Situation was on control , let's see what gonna happened.</t>
   </si>
 </sst>
 </file>
@@ -3208,48 +3214,96 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="8">
+        <v>46292</v>
+      </c>
+      <c r="B51" s="14">
+        <v>435</v>
+      </c>
+      <c r="C51" s="14">
+        <v>35</v>
+      </c>
+      <c r="D51" s="14">
+        <v>180</v>
+      </c>
+      <c r="E51" s="14">
+        <v>120</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>160</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+        <v>510</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B52" s="14">
+        <v>410</v>
+      </c>
+      <c r="C52" s="14">
+        <v>20</v>
+      </c>
+      <c r="D52" s="14">
+        <v>100</v>
+      </c>
+      <c r="E52" s="14">
+        <v>110</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>190</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>
